--- a/data/tenipuriwaza.xlsx
+++ b/data/tenipuriwaza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1264" documentId="8_{C623544B-A756-4537-BB3D-7090972E04C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DFECBCD-F8DD-47DF-8BD1-8F574F11CB62}"/>
+  <xr:revisionPtr revIDLastSave="1265" documentId="8_{C623544B-A756-4537-BB3D-7090972E04C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17E61273-A6CD-4820-B671-B71C08A5A63F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CCE97F10-6A64-4B3A-A256-1E7085600B75}"/>
   </bookViews>
@@ -5380,13 +5380,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>織田カズヤ</t>
-    <rPh sb="0" eb="2">
-      <t>オダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>阿修羅の神童</t>
     <rPh sb="0" eb="3">
       <t>アシュラ</t>
@@ -6592,6 +6585,10 @@
     <rPh sb="4" eb="6">
       <t>オオマガリ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>徳川カズヤ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9561,7 +9558,7 @@
         <v>389</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>390</v>
@@ -9585,7 +9582,7 @@
         <v>389</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>390</v>
@@ -9609,7 +9606,7 @@
         <v>389</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>393</v>
@@ -9630,7 +9627,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A105" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>12</v>
@@ -9657,7 +9654,7 @@
         <v>389</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>397</v>
@@ -12047,7 +12044,7 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A210" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>607</v>
@@ -12074,7 +12071,7 @@
         <v>607</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>609</v>
@@ -12095,7 +12092,7 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A212" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>607</v>
@@ -12119,7 +12116,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A213" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>607</v>
@@ -12143,7 +12140,7 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A214" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>167</v>
@@ -12167,7 +12164,7 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A215" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>167</v>
@@ -12194,7 +12191,7 @@
         <v>616</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>617</v>
@@ -12214,7 +12211,7 @@
         <v>616</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>617</v>
@@ -12234,7 +12231,7 @@
         <v>616</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>620</v>
@@ -12251,7 +12248,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A219" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>167</v>
@@ -12622,7 +12619,7 @@
         <v>655</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>656</v>
+        <v>828</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>653</v>
@@ -12643,7 +12640,7 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A236" s="2" t="s">
-        <v>656</v>
+        <v>828</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>655</v>
@@ -12652,7 +12649,7 @@
         <v>653</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>654</v>
@@ -12663,19 +12660,19 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A237" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>653</v>
       </c>
       <c r="D237" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E237" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
@@ -12683,45 +12680,45 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A238" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>653</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F238" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="G238" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="G238" s="2" t="s">
+      <c r="H238" s="3" t="s">
         <v>664</v>
-      </c>
-      <c r="H238" s="3" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A239" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="B239" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="B239" s="2" t="s">
+      <c r="C239" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D239" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="C239" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="D239" s="2" t="s">
+      <c r="E239" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>670</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>629</v>
@@ -12733,19 +12730,19 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A240" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="B240" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="B240" s="2" t="s">
-        <v>668</v>
-      </c>
       <c r="C240" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>629</v>
@@ -12757,22 +12754,22 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A241" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="B241" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="B241" s="2" t="s">
+      <c r="C241" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="D241" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="C241" s="2" t="s">
+      <c r="E241" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="D241" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>673</v>
-      </c>
       <c r="F241" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>630</v>
@@ -12781,19 +12778,19 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A242" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C242" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E242" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="D242" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>629</v>
@@ -12802,94 +12799,94 @@
         <v>630</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A243" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B243" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="B243" s="2" t="s">
+      <c r="C243" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="D243" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="C243" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>682</v>
-      </c>
       <c r="E243" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H243" s="2"/>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A244" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H244" s="2"/>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A245" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H245" s="2"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A246" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
@@ -12897,22 +12894,22 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A247" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>630</v>
@@ -12921,43 +12918,43 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A248" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H248" s="2"/>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A249" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="D249" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="B249" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="D249" s="2" t="s">
-        <v>695</v>
-      </c>
       <c r="E249" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>629</v>
@@ -12969,19 +12966,19 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A250" s="2" t="s">
-        <v>656</v>
+        <v>828</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
@@ -12989,43 +12986,43 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A251" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>656</v>
+        <v>828</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H251" s="2"/>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A252" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>629</v>
@@ -13035,19 +13032,19 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A253" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B253" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="D253" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>702</v>
       </c>
       <c r="F253" s="2"/>
       <c r="G253" s="2"/>
@@ -13055,43 +13052,43 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A254" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B254" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="B254" s="2" t="s">
+      <c r="C254" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D254" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="C254" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="D254" s="2" t="s">
+      <c r="E254" s="2" t="s">
         <v>706</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>707</v>
       </c>
       <c r="F254" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H254" s="2"/>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A255" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C255" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="D255" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="D255" s="2" t="s">
-        <v>710</v>
-      </c>
       <c r="E255" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>629</v>
@@ -13103,19 +13100,19 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A256" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>629</v>
@@ -13127,19 +13124,19 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A257" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F257" s="2" t="s">
         <v>629</v>
@@ -13151,19 +13148,19 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A258" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>629</v>
@@ -13175,19 +13172,19 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A259" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>629</v>
@@ -13199,67 +13196,67 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A260" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B260" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="B260" s="2" t="s">
-        <v>705</v>
-      </c>
       <c r="C260" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="D260" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="D260" s="2" t="s">
-        <v>717</v>
-      </c>
       <c r="E260" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H260" s="2"/>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A261" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H261" s="2"/>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A262" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B262" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="E262" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="D262" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>702</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>629</v>
@@ -13271,19 +13268,19 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A263" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D263" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B263" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="D263" s="2" t="s">
-        <v>722</v>
-      </c>
       <c r="E263" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F263" s="2"/>
       <c r="G263" s="2" t="s">
@@ -13293,19 +13290,19 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A264" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B264" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="E264" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="E264" s="2" t="s">
-        <v>702</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>629</v>
@@ -13317,19 +13314,19 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A265" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F265" s="2"/>
       <c r="G265" s="2" t="s">
@@ -13339,19 +13336,19 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A266" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>615</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>629</v>
@@ -13363,43 +13360,43 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A267" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C267" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="D267" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="D267" s="2" t="s">
+      <c r="E267" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>727</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H267" s="2"/>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A268" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B268" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="D268" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="C268" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>729</v>
-      </c>
       <c r="E268" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>629</v>
@@ -13411,19 +13408,19 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A269" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>629</v>
@@ -13435,19 +13432,19 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A270" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>629</v>
@@ -13459,19 +13456,19 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A271" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
@@ -13479,19 +13476,19 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A272" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C272" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D272" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="D272" s="2" t="s">
-        <v>732</v>
-      </c>
       <c r="E272" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
@@ -13502,25 +13499,25 @@
         <v>655</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.4">
@@ -13528,16 +13525,16 @@
         <v>655</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
@@ -13545,19 +13542,19 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A275" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C275" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D275" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="D275" s="2" t="s">
-        <v>736</v>
-      </c>
       <c r="E275" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
@@ -13565,43 +13562,43 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A276" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C276" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="D276" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="D276" s="2" t="s">
-        <v>743</v>
-      </c>
       <c r="E276" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H276" s="2"/>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A277" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C277" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="D277" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="D277" s="2" t="s">
-        <v>745</v>
-      </c>
       <c r="E277" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>629</v>
@@ -13613,19 +13610,19 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A278" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="D278" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="B278" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="D278" s="2" t="s">
+      <c r="E278" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="F278" s="2" t="s">
         <v>629</v>
@@ -13637,43 +13634,43 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A279" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B279" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="B279" s="2" t="s">
-        <v>753</v>
-      </c>
       <c r="C279" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="D279" s="7" t="s">
         <v>750</v>
       </c>
-      <c r="D279" s="7" t="s">
-        <v>751</v>
-      </c>
       <c r="E279" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H279" s="2"/>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A280" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="C280" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="B280" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="C280" s="2" t="s">
+      <c r="D280" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="D280" s="2" t="s">
-        <v>756</v>
-      </c>
       <c r="E280" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
@@ -13681,19 +13678,19 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A281" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
@@ -13701,19 +13698,19 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A282" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
@@ -13721,19 +13718,19 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A283" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F283" s="2" t="s">
         <v>629</v>
@@ -13745,19 +13742,19 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A284" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C284" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="D284" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="D284" s="2" t="s">
-        <v>761</v>
-      </c>
       <c r="E284" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
@@ -13765,19 +13762,19 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A285" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B285" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="B285" s="2" t="s">
-        <v>753</v>
-      </c>
       <c r="C285" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="D285" s="2" t="s">
-        <v>763</v>
-      </c>
       <c r="E285" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
@@ -13785,19 +13782,19 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A286" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B286" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="E286" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="D286" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
@@ -13805,67 +13802,67 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A287" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C287" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="E287" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="D287" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="E287" s="2" t="s">
-        <v>768</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H287" s="2"/>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A288" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H288" s="2"/>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A289" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="D289" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="B289" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="D289" s="2" t="s">
-        <v>772</v>
-      </c>
       <c r="E289" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
@@ -13873,93 +13870,93 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A290" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C290" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="B290" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>775</v>
-      </c>
       <c r="D290" s="7" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
       <c r="H290" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="291" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A291" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B291" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C291" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="C291" s="2" t="s">
-        <v>775</v>
-      </c>
       <c r="D291" s="9" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="292" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A292" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D292" s="9" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F292" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A293" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C293" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="D293" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="D293" s="2" t="s">
-        <v>778</v>
-      </c>
       <c r="E293" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
@@ -13967,19 +13964,19 @@
     </row>
     <row r="294" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A294" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C294" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="B294" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>781</v>
-      </c>
       <c r="D294" s="9" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F294" s="2" t="s">
         <v>629</v>
@@ -13988,50 +13985,50 @@
         <v>630</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="295" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A295" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B295" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C295" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="C295" s="2" t="s">
-        <v>781</v>
-      </c>
       <c r="D295" s="9" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F295" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="296" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A296" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C296" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="B296" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>781</v>
-      </c>
       <c r="D296" s="9" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>629</v>
@@ -14040,50 +14037,50 @@
         <v>630</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="297" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A297" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B297" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="C297" s="2" t="s">
-        <v>781</v>
-      </c>
       <c r="D297" s="9" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="298" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A298" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B298" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="C298" s="2" t="s">
-        <v>781</v>
-      </c>
       <c r="D298" s="9" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>629</v>
@@ -14092,50 +14089,50 @@
         <v>630</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="299" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A299" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C299" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="B299" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>781</v>
-      </c>
       <c r="D299" s="9" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A300" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C300" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="D300" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="D300" s="2" t="s">
-        <v>783</v>
-      </c>
       <c r="E300" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F300" s="2"/>
       <c r="G300" s="2"/>
@@ -14143,85 +14140,85 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A301" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F301" s="2"/>
       <c r="G301" s="2"/>
       <c r="H301" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="302" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A302" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C302" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D302" s="9" t="s">
         <v>787</v>
       </c>
-      <c r="D302" s="9" t="s">
-        <v>788</v>
-      </c>
       <c r="E302" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F302" s="2"/>
       <c r="G302" s="2"/>
       <c r="H302" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="303" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A303" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C303" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D303" s="9" t="s">
         <v>787</v>
       </c>
-      <c r="D303" s="9" t="s">
-        <v>788</v>
-      </c>
       <c r="E303" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F303" s="2"/>
       <c r="G303" s="2"/>
       <c r="H303" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A304" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="E304" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="D304" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="E304" s="2" t="s">
-        <v>795</v>
       </c>
       <c r="F304" s="2"/>
       <c r="G304" s="2"/>
@@ -14229,19 +14226,19 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A305" s="2" t="s">
-        <v>656</v>
+        <v>828</v>
       </c>
       <c r="B305" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="E305" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="D305" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="E305" s="2" t="s">
-        <v>795</v>
       </c>
       <c r="F305" s="2"/>
       <c r="G305" s="2"/>
@@ -14249,43 +14246,43 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A306" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="E306" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="D306" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="E306" s="2" t="s">
-        <v>795</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H306" s="2"/>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A307" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="E307" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="C307" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="D307" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="E307" s="2" t="s">
-        <v>795</v>
       </c>
       <c r="F307" s="2"/>
       <c r="G307" s="2"/>
@@ -14293,19 +14290,19 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A308" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B308" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="E308" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="C308" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="D308" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="E308" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="F308" s="2" t="s">
         <v>629</v>
@@ -14317,19 +14314,19 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A309" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B309" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E309" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="D309" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E309" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>629</v>
@@ -14341,19 +14338,19 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A310" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B310" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E310" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="D310" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="E310" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>629</v>
@@ -14365,19 +14362,19 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A311" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E311" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="C311" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="D311" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E311" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>629</v>
@@ -14389,46 +14386,46 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A312" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B312" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E312" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="C312" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="D312" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E312" s="2" t="s">
-        <v>766</v>
-      </c>
       <c r="F312" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="G312" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="G312" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="H312" s="2"/>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A313" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B313" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="E313" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="C313" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="D313" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="E313" s="2" t="s">
-        <v>766</v>
-      </c>
       <c r="F313" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>630</v>
@@ -14437,22 +14434,22 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A314" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B314" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="E314" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="C314" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="D314" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="E314" s="2" t="s">
-        <v>766</v>
-      </c>
       <c r="F314" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>630</v>
@@ -14461,48 +14458,48 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A315" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B315" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="E315" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="C315" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="D315" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="E315" s="2" t="s">
-        <v>766</v>
-      </c>
       <c r="F315" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>630</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A316" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B316" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="E316" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="C316" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="D316" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>766</v>
-      </c>
       <c r="F316" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>630</v>
@@ -14511,45 +14508,45 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A317" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E317" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="C317" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="D317" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="E317" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="F317" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A318" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="E318" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="C318" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="D318" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="F318" s="2" t="s">
         <v>629</v>
@@ -14561,19 +14558,19 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A319" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E319" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="C319" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="D319" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="E319" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>629</v>
@@ -14585,22 +14582,22 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A320" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C320" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="F320" s="2" t="s">
         <v>811</v>
-      </c>
-      <c r="D320" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="E320" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="F320" s="2" t="s">
-        <v>812</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>630</v>
@@ -14609,117 +14606,117 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A321" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B321" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C321" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="C321" s="2" t="s">
-        <v>815</v>
-      </c>
       <c r="D321" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F321" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="G321" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="G321" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="H321" s="2"/>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A322" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="E322" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="C322" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="D322" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="E322" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="F322" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H322" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A323" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F323" s="2" t="s">
         <v>629</v>
       </c>
       <c r="G323" s="2"/>
       <c r="H323" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A324" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F324" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="G324" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="G324" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="H324" s="2"/>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A325" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C325" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="D325" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="D325" s="2" t="s">
-        <v>822</v>
-      </c>
       <c r="E325" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F325" s="2"/>
       <c r="G325" s="2"/>
@@ -14727,22 +14724,22 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A326" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C326" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="D326" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="D326" s="2" t="s">
-        <v>824</v>
-      </c>
       <c r="E326" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>630</v>
